--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488056_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488056_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0663</v>
+        <v>0.7336</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9267</v>
+        <v>1.9309</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8603</v>
+        <v>-1.1973</v>
       </c>
       <c r="G2" t="n">
         <v>0.3168</v>
@@ -610,13 +610,13 @@
         <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6659</v>
+        <v>0.3332</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2814</v>
+        <v>0.2856</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3845</v>
+        <v>0.0476</v>
       </c>
       <c r="V2" t="n">
         <v>-0.511</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. SHERIFF</t>
+          <t>W. EL OTMANI MOHAMED</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1732</v>
+        <v>0.3692</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5181</v>
+        <v>2.6653</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3449</v>
+        <v>-2.2961</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.9371</v>
+        <v>-2.0096</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.7323</v>
+        <v>-2.006</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2048</v>
+        <v>-0.0036</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3335</v>
+        <v>1.2388</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3897</v>
+        <v>0.7333</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7232</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2705</v>
+        <v>-3.2484</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3426</v>
+        <v>-2.7393</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.928</v>
+        <v>-0.5091</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5682</v>
+        <v>0.1653</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4266</v>
+        <v>0.5564</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1416</v>
+        <v>-0.3911</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5331</v>
+        <v>0.4295</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7403</v>
+        <v>0.8701</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2071</v>
+        <v>-0.4406</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. EL OTMANI MOHAMED</t>
+          <t>D. SHERIFF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.7599</v>
+        <v>-0.6522</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9293</v>
+        <v>1.805</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6892</v>
+        <v>-2.4572</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.0096</v>
+        <v>-1.9371</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.006</v>
+        <v>-1.7323</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0036</v>
+        <v>-0.2048</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2388</v>
+        <v>0.3335</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7333</v>
+        <v>-0.3897</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.7232</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.2484</v>
+        <v>-2.2705</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.7393</v>
+        <v>-1.3426</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5091</v>
+        <v>-0.928</v>
       </c>
       <c r="P4" t="n">
-        <v>1.784</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R4" t="n">
-        <v>1.784</v>
+        <v>0.9911</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9638</v>
+        <v>1.7428</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1796</v>
+        <v>1.7135</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7842</v>
+        <v>0.0293</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4295</v>
+        <v>0.5331</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8701</v>
+        <v>1.7403</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4406</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CERISUELO QUESADA</t>
+          <t>J. VICENTE BOSCH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1552</v>
+        <v>-1.3893</v>
       </c>
       <c r="E5" t="n">
-        <v>0.194</v>
+        <v>1.0528</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3492</v>
+        <v>-2.4421</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0978</v>
+        <v>0.1431</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.7175</v>
+        <v>-1.6841</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6198</v>
+        <v>1.8272</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2216</v>
+        <v>1.87</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0207</v>
+        <v>0.0542</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2009</v>
+        <v>1.8158</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3194</v>
+        <v>-1.7269</v>
       </c>
       <c r="N5" t="n">
         <v>-1.7383</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4189</v>
+        <v>0.0114</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9911</v>
+        <v>1.3876</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5793</v>
+        <v>-0.4551</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3599</v>
+        <v>-0.0926</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2194</v>
+        <v>-0.3626</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6368</v>
+        <v>-1.4737</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6036</v>
+        <v>0.2666</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2403</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VICENTE BOSCH</t>
+          <t>J. CERISUELO QUESADA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6378</v>
+        <v>-1.7207</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8885999999999999</v>
+        <v>-0.3154</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.5264</v>
+        <v>-1.4054</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1431</v>
+        <v>-1.0978</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6841</v>
+        <v>-1.7175</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8272</v>
+        <v>0.6198</v>
       </c>
       <c r="J6" t="n">
-        <v>1.87</v>
+        <v>0.2216</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0542</v>
+        <v>0.0207</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8158</v>
+        <v>0.2009</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7269</v>
+        <v>-1.3194</v>
       </c>
       <c r="N6" t="n">
         <v>-1.7383</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0114</v>
+        <v>0.4189</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7036</v>
+        <v>0.0138</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2568</v>
+        <v>-0.1494</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4468</v>
+        <v>0.1632</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4737</v>
+        <v>-0.6368</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2666</v>
+        <v>0.6036</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7403</v>
+        <v>-1.2403</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5444</v>
+        <v>-2.8584</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3946</v>
+        <v>-0.3717</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1498</v>
+        <v>-2.4867</v>
       </c>
       <c r="G7" t="n">
         <v>-2.9408</v>
@@ -1000,13 +1000,13 @@
         <v>1.1893</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9757</v>
+        <v>0.6617</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6867</v>
+        <v>0.7096</v>
       </c>
       <c r="U7" t="n">
-        <v>0.289</v>
+        <v>-0.0479</v>
       </c>
       <c r="V7" t="n">
         <v>-0.7776</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.4896</v>
+        <v>-4.3877</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1008</v>
+        <v>0.001</v>
       </c>
       <c r="F8" t="n">
         <v>-4.3888</v>
@@ -1078,10 +1078,10 @@
         <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2666</v>
+        <v>1.3684</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3621</v>
+        <v>1.4639</v>
       </c>
       <c r="U8" t="n">
         <v>-0.0955</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.2278</v>
+        <v>-5.1934</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9829</v>
+        <v>-3.145</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2449</v>
+        <v>-2.0484</v>
       </c>
       <c r="G9" t="n">
         <v>-4.1015</v>
@@ -1156,13 +1156,13 @@
         <v>0.9911</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0142</v>
+        <v>0.0203</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3706</v>
+        <v>0.4673</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.447</v>
       </c>
       <c r="V9" t="n">
         <v>0.8701</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.444</v>
+        <v>-9.9003</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7325</v>
+        <v>-4.1607</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.7115</v>
+        <v>-5.7396</v>
       </c>
       <c r="G10" t="n">
         <v>-6.0545</v>
@@ -1234,13 +1234,13 @@
         <v>1.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1744</v>
+        <v>1.7181</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2483</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.102</v>
       </c>
       <c r="V10" t="n">
         <v>-4.9692</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-25.0192</v>
+        <v>-24.9992</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7541000000000011</v>
+        <v>-0.5378000000000007</v>
       </c>
       <c r="F11" t="n">
-        <v>-24.265</v>
+        <v>-24.4616</v>
       </c>
       <c r="G11" t="n">
         <v>-21.8162</v>
@@ -1285,13 +1285,13 @@
         <v>-10.0144</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0933</v>
+        <v>-2.093299999999999</v>
       </c>
       <c r="K11" t="n">
         <v>5.1152</v>
       </c>
       <c r="L11" t="n">
-        <v>-7.2085</v>
+        <v>-7.208499999999999</v>
       </c>
       <c r="M11" t="n">
         <v>-19.7228</v>
@@ -1303,7 +1303,7 @@
         <v>-2.8057</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1982000000000002</v>
+        <v>0.1982000000000004</v>
       </c>
       <c r="Q11" t="n">
         <v>-10.9021</v>
@@ -1312,19 +1312,19 @@
         <v>11.1005</v>
       </c>
       <c r="S11" t="n">
-        <v>5.5485</v>
+        <v>5.568499999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>6.558</v>
+        <v>6.7743</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0095</v>
+        <v>-1.206</v>
       </c>
       <c r="V11" t="n">
         <v>-8.9498</v>
       </c>
       <c r="W11" t="n">
-        <v>5.683599999999999</v>
+        <v>5.6836</v>
       </c>
       <c r="X11" t="n">
         <v>-14.6333</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.833399999999999</v>
+        <v>9.6812</v>
       </c>
       <c r="E12" t="n">
-        <v>9.5549</v>
+        <v>9.3512</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2785</v>
+        <v>0.3301</v>
       </c>
       <c r="G12" t="n">
         <v>6.3661</v>
@@ -1390,13 +1390,13 @@
         <v>1.9822</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.394</v>
+        <v>-0.5461</v>
       </c>
       <c r="T12" t="n">
-        <v>0.382</v>
+        <v>0.1782</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.776</v>
+        <v>-0.7244</v>
       </c>
       <c r="V12" t="n">
         <v>2.0772</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.5341</v>
+        <v>9.1022</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9348</v>
+        <v>6.6479</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5993</v>
+        <v>2.4543</v>
       </c>
       <c r="G13" t="n">
         <v>7.9343</v>
@@ -1468,13 +1468,13 @@
         <v>1.784</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4686</v>
+        <v>-0.9005</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7377</v>
+        <v>-0.0246</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7308</v>
+        <v>-0.8758</v>
       </c>
       <c r="V13" t="n">
         <v>1.4737</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.063</v>
+        <v>5.8723</v>
       </c>
       <c r="E14" t="n">
-        <v>5.8788</v>
+        <v>5.777</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1841</v>
+        <v>0.0953</v>
       </c>
       <c r="G14" t="n">
         <v>2.4185</v>
@@ -1546,13 +1546,13 @@
         <v>1.784</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.3239</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.117</v>
+        <v>-0.2058</v>
       </c>
       <c r="V14" t="n">
         <v>1.5441</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5982</v>
+        <v>4.3407</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4415</v>
+        <v>4.0527</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1567</v>
+        <v>0.288</v>
       </c>
       <c r="G15" t="n">
         <v>2.565</v>
@@ -1624,13 +1624,13 @@
         <v>0.9911</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2354</v>
+        <v>-0.4929</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4881</v>
+        <v>0.1231</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7472</v>
+        <v>-0.616</v>
       </c>
       <c r="V15" t="n">
         <v>1.2775</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6014</v>
+        <v>2.4597</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6218</v>
+        <v>1.3162</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9796</v>
+        <v>1.1435</v>
       </c>
       <c r="G16" t="n">
         <v>1.8676</v>
@@ -1702,13 +1702,13 @@
         <v>0.7929</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.275</v>
+        <v>-0.4167</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3782</v>
+        <v>0.0726</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6532</v>
+        <v>-0.4893</v>
       </c>
       <c r="V16" t="n">
         <v>1.2071</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5037</v>
+        <v>1.8817</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3218</v>
+        <v>2.4237</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8182</v>
+        <v>-0.542</v>
       </c>
       <c r="G17" t="n">
         <v>2.0765</v>
@@ -1780,13 +1780,13 @@
         <v>0.7929</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.659</v>
+        <v>-0.2809</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1176</v>
+        <v>0.2194</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7765</v>
+        <v>-0.5003</v>
       </c>
       <c r="V17" t="n">
         <v>1.4737</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5357</v>
+        <v>0.3554</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9295</v>
+        <v>-1.1332</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4651</v>
+        <v>1.4886</v>
       </c>
       <c r="G19" t="n">
         <v>1.3235</v>
@@ -1936,13 +1936,13 @@
         <v>0.7929</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3509</v>
+        <v>0.1706</v>
       </c>
       <c r="T19" t="n">
-        <v>0.514</v>
+        <v>0.3103</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1631</v>
+        <v>-0.1396</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9405</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0437</v>
+        <v>-0.0156</v>
       </c>
       <c r="E20" t="n">
         <v>-0.0624</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="G20" t="n">
         <v>0.1358</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1795</v>
+        <v>-0.1514</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1171</v>
+        <v>-0.089</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1273</v>
+        <v>-0.8769</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6017</v>
+        <v>0.3793</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.729</v>
+        <v>-1.2562</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8836000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5294</v>
+        <v>-0.2203</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2886</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7592</v>
+        <v>-0.2865</v>
       </c>
       <c r="V21" t="n">
         <v>1.6145</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7139</v>
+        <v>-1.6858</v>
       </c>
       <c r="E22" t="n">
         <v>-1.7326</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5433</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1795</v>
+        <v>-0.1514</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1171</v>
+        <v>-0.089</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3364</v>
+        <v>-3.3085</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4461</v>
+        <v>-1.8349</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8902</v>
+        <v>-1.4736</v>
       </c>
       <c r="G23" t="n">
         <v>-0.484</v>
@@ -2248,13 +2248,13 @@
         <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4648</v>
+        <v>-0.437</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6753</v>
+        <v>-0.0641</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7894</v>
+        <v>-0.3728</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6036</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>27.0509</v>
+        <v>28.40910000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>25.7874</v>
+        <v>25.7876</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2633</v>
+        <v>2.6216</v>
       </c>
       <c r="G24" t="n">
         <v>23.3791</v>
@@ -2326,13 +2326,13 @@
         <v>10.9023</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.460900000000001</v>
+        <v>-3.1027</v>
       </c>
       <c r="T24" t="n">
-        <v>1.2861</v>
+        <v>1.286</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.746599999999999</v>
+        <v>-4.388500000000001</v>
       </c>
       <c r="V24" t="n">
         <v>9.123699999999999</v>
